--- a/AAII_Financials/Yearly/AVGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AVGO_YR_FIN.xlsx
@@ -4096,19 +4096,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>713000</v>
+        <v>574000</v>
       </c>
       <c r="E83" s="3">
-        <v>743000</v>
+        <v>593000</v>
       </c>
       <c r="F83" s="3">
-        <v>588000</v>
+        <v>502000</v>
       </c>
       <c r="G83" s="3">
-        <v>625000</v>
+        <v>529000</v>
       </c>
       <c r="H83" s="3">
-        <v>638000</v>
+        <v>539000</v>
       </c>
       <c r="I83" s="3">
         <v>570000</v>
